--- a/shared/registro_cortes.xlsx
+++ b/shared/registro_cortes.xlsx
@@ -1398,22 +1398,22 @@
       <c r="E22" s="22" t="inlineStr"/>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>CORTADO</t>
+          <t>EXONERADO</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>Corte físico confirmado 2026-06</t>
+          <t>No corresponde: salio en corte por falta de pago, pero el pago SI existia -- Wagner Trujillo (cobrador) lo retuvo en su yape personal en junio y lo recupero en efectivo recien en julio. Registrado en abonos_rezagados.xlsx (S/71, MES_ANO_APLICA=2026-07). Reclamo del propio vecino confirmado 28/07/2026 (notas_2026-07.xlsx).</t>
         </is>
       </c>
       <c r="H22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="I22" s="24" t="inlineStr">
         <is>
-          <t>seguimiento.py</t>
+          <t>manual/supervisor</t>
         </is>
       </c>
     </row>
